--- a/Produkty/321-50074321.xlsx
+++ b/Produkty/321-50074321.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -430,13 +430,22 @@
       <c r="J1" t="str">
         <v>Stanowisko</v>
       </c>
+      <c r="K1" t="str">
+        <v>Ilość</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Grupa</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Priorytet</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v/>
       </c>
       <c r="B2" t="str">
-        <v>1000xx60x28-321</v>
+        <v>1000xx60x28</v>
       </c>
       <c r="C2" t="str">
         <v>1000</v>
@@ -461,6 +470,15 @@
       </c>
       <c r="J2" t="str">
         <v>2</v>
+      </c>
+      <c r="K2" t="str">
+        <v>1</v>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
@@ -468,7 +486,7 @@
         <v/>
       </c>
       <c r="B3" t="str">
-        <v>820x60x28-321</v>
+        <v>820x60x28</v>
       </c>
       <c r="C3" t="str">
         <v>820</v>
@@ -493,6 +511,15 @@
       </c>
       <c r="J3" t="str">
         <v>2</v>
+      </c>
+      <c r="K3" t="str">
+        <v>2</v>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -500,7 +527,7 @@
         <v/>
       </c>
       <c r="B4" t="str">
-        <v>760x25x28-321</v>
+        <v>760x25x28</v>
       </c>
       <c r="C4" t="str">
         <v>760</v>
@@ -525,6 +552,15 @@
       </c>
       <c r="J4" t="str">
         <v>2</v>
+      </c>
+      <c r="K4" t="str">
+        <v>1</v>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -532,7 +568,7 @@
         <v/>
       </c>
       <c r="B5" t="str">
-        <v>710x25x28-321</v>
+        <v>710x25x28</v>
       </c>
       <c r="C5" t="str">
         <v>710</v>
@@ -557,11 +593,20 @@
       </c>
       <c r="J5" t="str">
         <v>2</v>
+      </c>
+      <c r="K5" t="str">
+        <v>1</v>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
   </ignoredErrors>
 </worksheet>
 </file>